--- a/extenbooks/S309_extenbook.xlsx
+++ b/extenbooks/S309_extenbook.xlsx
@@ -14501,7 +14501,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -15645,11 +15645,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15672,88 +15672,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Luxury Good (x2) Demand Curves, Four Different Micro Foundations</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S309_research.json", "adequacy_report": "Technical/docs/chapters/CH3_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S309_DPR.md", "epr": "Technical/docs/series/S309_EPR.md", "loader": "Technical/code/L01_loaders/L01_S309_load.py", "processor": "Technical/code/P02_processors/P02_S309_construct.py", "validator": "Technical/code/V03_validators/V03_S309_validate.py", "processed": "Technical/data/processed/S309.parquet", "chopped_csv": "Technical/chopped/S309.csv", "extenbook_xlsx": "Technical/extenbooks/S309_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S309-A", "S309-B", "S309-C", "S309-D", "S309-E"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["SHAIKH_2016_EQ_3_4_3_11", "SHAIKH_2016_NETLOGO_SIMS"]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S309_extenbook.xlsx
+++ b/extenbooks/S309_extenbook.xlsx
@@ -2840,7 +2840,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8268,7 +8268,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8452,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9625,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9924,7 +9924,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -9993,7 +9993,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10131,7 +10131,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10660,7 +10660,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10683,7 +10683,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10867,7 +10867,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11097,7 +11097,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11120,7 +11120,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11166,7 +11166,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11281,7 +11281,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11419,7 +11419,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11442,7 +11442,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11511,7 +11511,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11672,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11764,7 +11764,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11879,7 +11879,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11925,7 +11925,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11948,7 +11948,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11971,7 +11971,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12040,7 +12040,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12201,7 +12201,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12247,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12454,7 +12454,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12546,7 +12546,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12592,7 +12592,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12615,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12661,7 +12661,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12707,7 +12707,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12730,7 +12730,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12753,7 +12753,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12822,7 +12822,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12868,7 +12868,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12937,7 +12937,7 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -12983,7 +12983,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13006,7 +13006,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13167,7 +13167,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13282,7 +13282,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13374,7 +13374,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13397,7 +13397,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13466,7 +13466,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13489,7 +13489,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13581,7 +13581,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13604,7 +13604,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13627,7 +13627,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13650,7 +13650,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13673,7 +13673,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13696,7 +13696,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13719,7 +13719,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13765,7 +13765,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13903,7 +13903,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13926,7 +13926,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13949,7 +13949,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13972,7 +13972,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -13995,7 +13995,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14018,7 +14018,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14064,7 +14064,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14087,7 +14087,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14133,7 +14133,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14156,7 +14156,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14202,7 +14202,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14248,7 +14248,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14271,7 +14271,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14432,7 +14432,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>x2_aggregate_demand_model_units</t>
+          <t>x2_per_agent_demand_model_units</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A118"/>
+  <dimension ref="A1:A123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -14487,7 +14487,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Record type**: Data Provenance Record</t>
         </is>
       </c>
     </row>
@@ -14522,7 +14522,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-wave-a-ch3 (Phase 5-8 fanout)</t>
+          <t>**Prepared by**: RSCD data-construction pipeline</t>
         </is>
       </c>
     </row>
@@ -14536,7 +14536,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>- Research dossier: `Technical/research/S309_research.json`</t>
+          <t>- Series research notes: `Technical/research/S309_research.json`</t>
         </is>
       </c>
     </row>
@@ -14617,7 +14617,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>## From the Book</t>
         </is>
       </c>
     </row>
@@ -14627,90 +14627,86 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+          <t>&gt; Despite their differences, all of the models give rise to the very same aggregate patterns. The essential point is that the same macroscopic patterns can obtain from a great variety of individual behaviors.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>|---|---|---|---|---|</t>
+          <t>&gt; -- Shaikh (2016), Chapter 3, p. 90 &lt;!-- kb: ch03, p.90 (ch03_micro_foundations.md, robust insensitivity) --&gt;</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>| **S309-A** | n/a | Shaikh 2016 eq (3.6) with y=200, c=0.5, x1min=10, p1=1; p2 sweep 2.0-&gt;3.0 | aggregate x2 | analytic regeneration |</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>| **S309-B** | n/a | NetLogo Neoclassical Homogeneous | aggregate x2 | tabulated from printed Fig 3.11 |</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>| **S309-C** | n/a | NetLogo Neoclassical Heterogeneous | aggregate x2 | tabulated from printed Fig 3.11 |</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>| **S309-D** | n/a | NetLogo Whimsical (Becker) | aggregate x2 | tabulated from printed Fig 3.11 |</t>
+          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>| **S309-E** | n/a | NetLogo Imitate-Innovate (Dosi) | aggregate x2 | tabulated from printed Fig 3.11 |</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>| **S309-A** (one of the dataset's data columns) | n/a | Shaikh 2016 eq (3.6) with y=200, c=0.5, x1min=10, p1=1; p2 sweep 2.0-&gt;3.0 | aggregate x2 | analytic regeneration |</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>| **S309-B** | n/a | NetLogo Neoclassical Homogeneous | aggregate x2 | tabulated from printed Fig 3.11 |</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>| **S309-C** | n/a | NetLogo Neoclassical Heterogeneous | aggregate x2 | tabulated from printed Fig 3.11 |</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1. Price grid: p2 in {2.00, 2.01, ..., 3.00}, 101 points.</t>
+          <t>| **S309-D** | n/a | NetLogo Whimsical (Becker) | aggregate x2 | tabulated from printed Fig 3.11 |</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2. **Theoretical (S309-A)**: eq (3.6) `x2 = c * (y - p1*x1min) / p2` with y=200, c=0.5, x1min=10, p1=1, so x2 = 0.5 * 190 / p2 = 95/p2. At p2=2: x2 = 47.5. At p2=3: x2 = 31.67. Hyperbolic shape, decreasing.</t>
+          <t>| **S309-E** | n/a | NetLogo Imitate-Innovate (Dosi) | aggregate x2 | tabulated from printed Fig 3.11 |</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>3. **Four NetLogo curves (S309-B..E)**: tabulated from printed Fig 3.11 with same per-model offsets as S308 (consistent visual spread per the printed figure).</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4. The chopped CSV has 5*101 = 505 rows.</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
@@ -14720,54 +14716,58 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>**Formula (theoretical only)**: `x2 = c * (y - p1*x1min) / p2`</t>
+          <t>1. Price grid: p2 in {2.00, 2.01, ..., 3.00}, 101 points.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2. **Theoretical (S309-A)**: eq (3.6) `x2 = c * (y - p1*x1min) / p2` with y=200, c=0.5, x1min=10, p1=1, so x2 = 0.5 * 190 / p2 = 95/p2. At p2=2: x2 = 47.5. At p2=3: x2 = 31.67. Hyperbolic shape, decreasing.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>3. **Four NetLogo curves (S309-B..E)**: tabulated from printed Fig 3.11 with same per-model offsets as S308 (consistent visual spread per the printed figure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4. The chopped CSV has 5*101 = 505 rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>**Formula (theoretical only)**: `x2 = c * (y - p1*x1min) / p2`</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>- **No year dimension**. Five curves indexed by p2 in [2.0, 3.0].</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>## 6. Units</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-    </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>- **Output**: aggregate luxury-good demand x2 in model units (range [30, 50] per printed Fig 3.11 y-axis).</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>- **x-axis**: price p2 (model currency).</t>
+          <t>- **No year dimension**. Five curves indexed by p2 in [2.0, 3.0].</t>
         </is>
       </c>
     </row>
@@ -14777,7 +14777,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -14787,126 +14787,122 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1. Same NetLogo tabulation caveat as S308. Random seeds unknown; Monte-Carlo not re-simulated.</t>
+          <t>- **Output**: aggregate luxury-good demand x2 in model units (range [30, 50] per printed Fig 3.11 y-axis).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2. The theoretical curve is hyperbolic (x2 = 95/p2), which gives elasticity exactly -1; Table 3.1's reported simulation elasticities (around -1.00 to -1.04) are consistent with this.</t>
+          <t>- **x-axis**: price p2 (model currency).</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>3. No proxy; no synthetic fill.</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>## 7. Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>## 8. Cross-references</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1. Same NetLogo tabulation caveat as S308. Random seeds unknown; Monte-Carlo not re-simulated.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: none</t>
+          <t>2. The theoretical curve is hyperbolic (x2 = 95/p2), which gives elasticity exactly -1; Table 3.1's reported simulation elasticities (around -1.00 to -1.04) are consistent with this.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 3, Fig3.11 on p. 100</t>
+          <t>3. No proxy; no synthetic fill.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>- **Knowledge Base**: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json` -&gt; Fig3.11</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>## 8. Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>## 9. Validation expectation</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>- **Predecessor series**: none (first constructed in this dataset).</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>- **Tolerance**: PASS_THEORETICAL. Per-subseries: monotone declining, values within [30, 50]. Cross-curve: all NetLogo curves within +/-2 percent of theoretical.</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 3, Fig3.11 on p. 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>- **Knowledge Base**: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json` -&gt; Fig3.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>- **Source-book text**: Shaikh (2016) Chapter 3, extracted in the project knowledge base (ch03_micro_foundations.md).</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4">
+      <c r="A74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>- **Tolerance**: the validator's theoretical-curve mode (checks the curve's shape and bounds rather than matching tabulated values). Per-subseries: monotone declining, values within [30, 50]. Cross-curve: all NetLogo curves within +/-2 percent of theoretical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4">
         <f>== EPR: S309_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t># S309 -- Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>**Series**: S309 -- Luxury Good (x2) Demand Curves, Four Different Micro Foundations</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>**Content type**: `theoretical`</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>**Related**: `S309_DPR.md`, `Technical/research/S309_research.json`</t>
+          <t># S309 -- Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -14916,27 +14912,35 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Series**: S309 -- Luxury Good (x2) Demand Curves, Four Different Micro Foundations</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>**Record type**: Extension Provenance Record</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>## 1. Classification</t>
+          <t>**Content type**: `theoretical`</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>`theoretical` (composite). No extension.</t>
+          <t>**Related**: `S309_DPR.md`, `Technical/research/S309_research.json`</t>
         </is>
       </c>
     </row>
@@ -14946,7 +14950,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>## 2. Method</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -14956,7 +14960,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>**Extension method**: `none`. Static regeneration each run.</t>
+          <t>## 1. Classification</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14970,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>## 3. Worked example</t>
+          <t>`theoretical` (composite). No extension.</t>
         </is>
       </c>
     </row>
@@ -14976,7 +14980,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>x2_theoretical = 95/p2. At p2=2.0: 47.5; at p2=3.0: 31.67. Elasticity = -1 (hyperbolic).</t>
+          <t>## 2. Method</t>
         </is>
       </c>
     </row>
@@ -14986,7 +14990,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>## 4. No-Proxy disclosure</t>
+          <t>**Extension method**: `none`. Static regeneration each time the data-loading step runs.</t>
         </is>
       </c>
     </row>
@@ -14996,7 +15000,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>No proxy substitution. See `S309_DPR.md` for source details.</t>
+          <t>## 3. Worked example</t>
         </is>
       </c>
     </row>
@@ -15006,7 +15010,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>## 5. No-Synthetic disclosure</t>
+          <t>x2_theoretical = 95/p2. At p2=2.0: 47.5; at p2=3.0: 31.67. Elasticity = -1 (hyperbolic).</t>
         </is>
       </c>
     </row>
@@ -15016,86 +15020,109 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>No synthetic gap-filling in the prohibited sense. The DPR documents any</t>
+          <t>## 4. No-Proxy disclosure</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>analytic regeneration or library-data dependence explicitly.</t>
-        </is>
-      </c>
+      <c r="A104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>No proxy substitution. See `S309_DPR.md` for source details.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>## 5. No-Synthetic disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>No synthetic gap-filling in the prohibited sense. The companion Data Provenance Record (DPR) documents any analytic regeneration or library-data dependence explicitly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>## 6. Failure-mode table</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>Same as S308; NetLogo source unavailable.</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>No CD2 predecessor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr"/>
-    </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>## 8. Why no API extension applies</t>
-        </is>
-      </c>
+      <c r="A114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>## 7. Predecessor divergence pre-disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>This series has no time dimension (theoretical/cross_sectional). The</t>
-        </is>
-      </c>
+      <c r="A116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>Predecessor series: none (first constructed in this dataset).</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>## 8. Why no API extension applies</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>This series has no time dimension (theoretical/cross_sectional). The</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
           <t>Anu-framework rule on extension only applies to `time_series` series. The</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>chopped CSV is the final published deliverable.</t>
         </is>
@@ -15477,7 +15504,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -15618,7 +15645,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-05-18T22:02:24.984873+00:00</t>
+          <t>2026-07-02T06:22:26.980476+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S309_extenbook.xlsx
+++ b/extenbooks/S309_extenbook.xlsx
@@ -14501,7 +14501,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: theoretical_validated</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-02T06:22:26.980476+00:00</t>
+          <t>2026-07-11T03:44:24.709908+00:00</t>
         </is>
       </c>
     </row>
@@ -15672,11 +15672,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15699,6 +15699,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2016_NETLOGO_SIMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>theoretical_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Renderable multi-trace demand curve (Shaikh Fig 3.11): one analytic curve plus four NetLogo agent-based simulation curves for the luxury good, on shared price-quantity axes (5 subseries x 101 points = 505 rows, all non-null). Renders as overlaid x-y demand curves (x = aggregate x2 quantity, carried in the 'year' index column 1-99, NOT calendar years). TRIAGE_PRESCREEN EMPTY flag is STALE: L01_S309/P02_S309 exist and replicate.py --series S309 builds the chopped (PASS, 505 rows). content_type theoretical, construction composite. KB coverage: ch03 IS extracted in the book KB (HDARP v3.3 Sraffa OCR campaign) (Body_Text/ch03_micro_foundations.md + Figures/ch03/ch03_fig_3.11.md); the chapter-3 figure quotes in the research JSON ARE verifiable against KB, and a 'From the book' section can be populated in the explainer (doc-side backfill).", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S309_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S309_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Composite: one analytic curve + four NetLogo simulation curves overlaid on one figure. L01 tabulates each curve at the discrete price grid Shaikh used (step 0.01 over the published range). Per the playbook for theoretical series, NetLogo curves are tabulated from the printed-figure axis ranges; Shaikh's central claim is that micro foundations do not matter, so all four curves are expected to lie close to the theoretical curve and to each other (which is what the printed figure shows). Random seeds are not stated; exact statistical reproduction is impossible. | UNITS CORRECTION (SWEEP-ch0304, 2026-07-02): the x-axis is a PER-AGENT (representative-agent) quantity from eq 3.5 with income y=200, NOT an aggregate over 5000 agents/$1,000,000 as the prior units string implied; values unchanged (relabel only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>price p2 (model currency) vs per-agent x2 quantity (model units); representative agent, income y=200 (Shaikh eq 3.5) - NOT aggregated over a 5000-agent population</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
